--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260615.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260615.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>13.40%</t>
+          <t>13.74%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.03%</t>
+          <t>10.38%</t>
         </is>
       </c>
     </row>
@@ -660,51 +660,51 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.40%</t>
+          <t>6.25%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>力成科技</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>22,138,000</t>
+          <t>1,764,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.68%</t>
+          <t>5.57%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>力成科技</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>1,764,000</t>
+          <t>22,138,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.24%</t>
+          <t>5.17%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.67%</t>
+          <t>4.76%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.86%</t>
+          <t>4.10%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.95%</t>
+          <t>2.99%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>2.80%</t>
         </is>
       </c>
     </row>
@@ -814,51 +814,51 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>2.65%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>文曄科技</t>
+          <t>聖暉工程</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>15,276,000</t>
+          <t>2,827,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.58%</t>
+          <t>2.54%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>聖暉工程</t>
+          <t>文曄科技</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>2,827,000</t>
+          <t>15,276,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>2.47%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>2.44%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>2.34%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.18%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>1.91%</t>
         </is>
       </c>
     </row>
@@ -968,51 +968,51 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>1.87%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>仁寶電腦</t>
+          <t>中美矽晶</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>66,656,000</t>
+          <t>14,856,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.85%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>中美矽晶</t>
+          <t>仁寶電腦</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>14,856,000</t>
+          <t>66,656,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.80%</t>
         </is>
       </c>
     </row>
@@ -1034,68 +1034,68 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.69%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>和碩聯合</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>23,608,000</t>
+          <t>19,861,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.53%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>日電貿股</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>19,861,000</t>
+          <t>7,181,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.44%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>順達科技</t>
+          <t>和碩聯合</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>4,558,000</t>
+          <t>23,608,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1107,22 +1107,22 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>日電貿股</t>
+          <t>順達科技</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>7,181,000</t>
+          <t>4,558,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.40%</t>
         </is>
       </c>
     </row>
@@ -1144,24 +1144,24 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.32%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>可成科技</t>
+          <t>頎邦科技</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>7,631,000</t>
+          <t>6,921,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,110 +1173,110 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>頎邦科技</t>
+          <t>可成科技</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>6,921,000</t>
+          <t>7,631,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>202607WTX</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>115/07台股期貨</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>1,512,548,765</t>
+          <t>160</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>202606WTX</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>115/06台股期貨</t>
+          <t>家登精密</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>2,697,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>家登精密</t>
+          <t>牧德科技</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2,697,000</t>
+          <t>1,868,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>牧德科技</t>
+          <t>聯強國際</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>1,868,000</t>
+          <t>14,453,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
@@ -1298,95 +1298,95 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>聯強國際</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>14,453,000</t>
+          <t>940,774,378</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.67%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>群光電子</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>6,681,000</t>
+          <t>856,442,021</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.61%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>可寧衛股</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>893,352,462</t>
+          <t>29,406,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>可寧衛股</t>
+          <t>群光電子</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>29,406,000</t>
+          <t>6,681,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
@@ -1452,51 +1452,51 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>6188</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>廣明光電</t>
+          <t>義隆電子</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>7,462,000</t>
+          <t>4,075,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>6188</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>義隆電子</t>
+          <t>廣明光電</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>4,075,000</t>
+          <t>7,462,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.37%</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.31%</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.28%</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.18%</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.16%</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>-218,837,757</t>
+          <t>-191,896,344</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>-0.14%</t>
         </is>
       </c>
     </row>
